--- a/data/gold/results/table_1.xlsx
+++ b/data/gold/results/table_1.xlsx
@@ -415,22 +415,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>6293.083293176651</v>
+        <v>4875.04189130478</v>
       </c>
       <c r="C2">
-        <v>3129.438454051277</v>
+        <v>5595.226019299745</v>
       </c>
       <c r="D2">
-        <v>57.49180799643617</v>
+        <v>43.01963532551069</v>
       </c>
       <c r="E2">
-        <v>3515.40410784478</v>
+        <v>3833.21048095657</v>
       </c>
       <c r="F2">
-        <v>1067.400314520272</v>
+        <v>1481.801246893921</v>
       </c>
       <c r="G2">
-        <v>35271.23170522282</v>
+        <v>40596.97766008925</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -438,22 +438,22 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>4779.046706649486</v>
+        <v>1983.396441030832</v>
       </c>
       <c r="C3">
-        <v>1840.176537998628</v>
+        <v>1861.983933522006</v>
       </c>
       <c r="D3">
-        <v>38.07090316673552</v>
+        <v>16.23503612216632</v>
       </c>
       <c r="E3">
-        <v>2647.618898275895</v>
+        <v>1653.666331477455</v>
       </c>
       <c r="F3">
-        <v>789.4235870070347</v>
+        <v>550.6047532986458</v>
       </c>
       <c r="G3">
-        <v>32641.29746453972</v>
+        <v>37552.28493467391</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -461,22 +461,22 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>754.1175523753257</v>
+        <v>1339.915588010944</v>
       </c>
       <c r="C4">
-        <v>1129.661499993992</v>
+        <v>2924.042064732495</v>
       </c>
       <c r="D4">
-        <v>17.08442410567785</v>
+        <v>20.05719459529767</v>
       </c>
       <c r="E4">
-        <v>752.9042888256793</v>
+        <v>1646.700904396185</v>
       </c>
       <c r="F4">
-        <v>220.7972212611156</v>
+        <v>700.9609017771467</v>
       </c>
       <c r="G4">
-        <v>1730.881507198513</v>
+        <v>1950.307677832142</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -484,22 +484,22 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>180.5321341518415</v>
+        <v>921.1918622629997</v>
       </c>
       <c r="C5">
-        <v>134.3999160586708</v>
+        <v>781.6681210452316</v>
       </c>
       <c r="D5">
-        <v>2.161480724022677</v>
+        <v>6.536304608046691</v>
       </c>
       <c r="E5">
-        <v>113.2403207432043</v>
+        <v>531.0508450829358</v>
       </c>
       <c r="F5">
-        <v>57.17950625212023</v>
+        <v>230.2355918181278</v>
       </c>
       <c r="G5">
-        <v>899.0527334845993</v>
+        <v>1094.385047583204</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -530,7 +530,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -553,16 +553,16 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>553.8869</v>
+        <v>606.2380000000001</v>
       </c>
       <c r="C8">
-        <v>25.2005</v>
+        <v>27.5319</v>
       </c>
       <c r="D8">
-        <v>0.175</v>
+        <v>0.1911</v>
       </c>
       <c r="E8">
-        <v>1.6406</v>
+        <v>1.7924</v>
       </c>
       <c r="F8">
         <v>0</v>
